--- a/example-zh-tw.xlsx
+++ b/example-zh-tw.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qp/chatgpt/rack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BBDC900-9CA6-2A43-A74A-BA99EDDC4D36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A9E55F-3D6F-9E40-9C1C-F50BDF270521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16860" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16860" activeTab="1" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
   </bookViews>
   <sheets>
-    <sheet name="设备列表" sheetId="1" r:id="rId1"/>
-    <sheet name="模板说明" sheetId="2" r:id="rId2"/>
+    <sheet name="設備清單" sheetId="1" r:id="rId1"/>
+    <sheet name="範本說明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,150 +37,146 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
-  <si>
-    <t>设备名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始U位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结束U位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜4</t>
-  </si>
-  <si>
-    <t>机柜5</t>
-  </si>
-  <si>
-    <t>机柜7</t>
-  </si>
-  <si>
-    <t>机柜8</t>
-  </si>
-  <si>
-    <t>设备1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备2</t>
-  </si>
-  <si>
-    <t>设备3</t>
-  </si>
-  <si>
-    <t>设备4</t>
-  </si>
-  <si>
-    <t>设备7</t>
-  </si>
-  <si>
-    <t>设备8</t>
-  </si>
-  <si>
-    <t>设备9</t>
-  </si>
-  <si>
-    <t>设备11</t>
-  </si>
-  <si>
-    <t>设备12</t>
-  </si>
-  <si>
-    <t>设备13</t>
-  </si>
-  <si>
-    <t>设备14</t>
-  </si>
-  <si>
-    <t>机柜2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存储设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台式机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>说明文字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安全设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备5</t>
-  </si>
-  <si>
-    <t>设备6</t>
-  </si>
-  <si>
-    <t>设备10</t>
-  </si>
-  <si>
-    <t>机柜6</t>
-  </si>
-  <si>
-    <t>机柜3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜1</t>
-  </si>
-  <si>
-    <t>http://rack.szqp.site</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜图生成器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>型号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序列号</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+  <si>
+    <t>設備名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機櫃名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始U位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>結束U位置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機櫃1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機櫃4</t>
+  </si>
+  <si>
+    <t>機櫃5</t>
+  </si>
+  <si>
+    <t>機櫃7</t>
+  </si>
+  <si>
+    <t>機櫃8</t>
+  </si>
+  <si>
+    <t>設備1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設備2</t>
+  </si>
+  <si>
+    <t>設備3</t>
+  </si>
+  <si>
+    <t>設備4</t>
+  </si>
+  <si>
+    <t>設備7</t>
+  </si>
+  <si>
+    <t>設備8</t>
+  </si>
+  <si>
+    <t>設備9</t>
+  </si>
+  <si>
+    <t>設備11</t>
+  </si>
+  <si>
+    <t>設備12</t>
+  </si>
+  <si>
+    <t>設備13</t>
+  </si>
+  <si>
+    <t>設備14</t>
+  </si>
+  <si>
+    <t>機櫃2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設備類型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伺服器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>儲存設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>網路設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型機</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桌上型電腦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設備說明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>說明文字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資安設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設備5</t>
+  </si>
+  <si>
+    <t>設備6</t>
+  </si>
+  <si>
+    <t>設備10</t>
+  </si>
+  <si>
+    <t>機櫃6</t>
+  </si>
+  <si>
+    <t>機櫃3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機櫃1</t>
+  </si>
+  <si>
+    <t>機櫃圖產生器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>型號</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序號</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -204,11 +200,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>核心存储</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易主机</t>
+    <t>核心儲存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易主機</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -221,7 +217,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>模板使用说明：</t>
+      <t>範本使用說明：</t>
     </r>
     <r>
       <rPr>
@@ -243,7 +239,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>1. 请确保根据”</t>
+      <t>1. 請依照「</t>
     </r>
     <r>
       <rPr>
@@ -254,7 +250,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>设备列表</t>
+      <t>設備清單</t>
     </r>
     <r>
       <rPr>
@@ -264,7 +260,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“Sheet的列进行填写，每行填写一个设备的信息。
+      <t>」工作表的欄位填寫，每列填寫一台設備的資料。
 2.</t>
     </r>
     <r>
@@ -276,7 +272,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>”型号“</t>
+      <t>「型號」</t>
     </r>
     <r>
       <rPr>
@@ -297,7 +293,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>”序列号“</t>
+      <t>「序號」</t>
     </r>
     <r>
       <rPr>
@@ -307,7 +303,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>，”</t>
+      <t>，「</t>
     </r>
     <r>
       <rPr>
@@ -318,7 +314,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>设备说明</t>
+      <t>設備說明</t>
     </r>
     <r>
       <rPr>
@@ -328,8 +324,8 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“列可留空，其他列都需填写完整。
-3. 设备的用途等说明内容可填写在”</t>
+      <t>」欄位可留白，其餘欄位皆須完整填寫。
+3. 設備用途等說明可填寫於「</t>
     </r>
     <r>
       <rPr>
@@ -340,7 +336,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>设备说明</t>
+      <t>設備說明</t>
     </r>
     <r>
       <rPr>
@@ -350,9 +346,9 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“列，但考虑到美观，不宜填写过多内容。
-4. 设备的开始和结束U位不能重叠或冲突，不支持同一个U部署多个设备。若设备U位存在冲突，上传后会提示冲突设备。
-5.默认的设备类型包括”</t>
+      <t>」欄位，為維持版面美觀，內容不宜過多。
+4. 設備的起始與結束U位置不可重疊或衝突，同一個U位置僅能安裝一台設備。若U位置有衝突，上傳後會顯示發生衝突的設備。
+5.預設設備類型包括「</t>
     </r>
     <r>
       <rPr>
@@ -363,7 +359,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>服务器</t>
+      <t>伺服器</t>
     </r>
     <r>
       <rPr>
@@ -373,7 +369,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>」、「</t>
     </r>
     <r>
       <rPr>
@@ -384,7 +380,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>存储设备</t>
+      <t>儲存設備</t>
     </r>
     <r>
       <rPr>
@@ -394,7 +390,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>」、「</t>
     </r>
     <r>
       <rPr>
@@ -405,7 +401,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>网络设备</t>
+      <t>網路設備</t>
     </r>
     <r>
       <rPr>
@@ -415,7 +411,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>」、「</t>
     </r>
     <r>
       <rPr>
@@ -426,7 +422,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>安全设</t>
+      <t>資安設</t>
     </r>
     <r>
       <rPr>
@@ -436,7 +432,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>备</t>
+      <t>備</t>
     </r>
     <r>
       <rPr>
@@ -446,7 +442,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>」、「</t>
     </r>
     <r>
       <rPr>
@@ -457,7 +453,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>小型机</t>
+      <t>小型機</t>
     </r>
     <r>
       <rPr>
@@ -467,7 +463,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“，不属于这四种的会被归类为”</t>
+      <t>」，不屬於上述類型的設備會歸類為「</t>
     </r>
     <r>
       <rPr>
@@ -488,9 +484,9 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“，不同设备类型会对应不同的颜色，可以在机柜图生成器页面自定义颜色和增加更多分类。
-6.默认输出的布局图每排5个机柜，每个机柜42U，可在在机柜图生成器页面自定义。
-7.模板”</t>
+      <t>」。不同設備類型以不同顏色表示，可在機櫃圖產生器頁面自訂顏色及新增分類。
+6.預設輸出的配置圖每排5個機櫃，每個機櫃42U，可在機櫃圖產生器頁面自訂。
+7.範本「</t>
     </r>
     <r>
       <rPr>
@@ -501,7 +497,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>设备列表</t>
+      <t>設備清單</t>
     </r>
     <r>
       <rPr>
@@ -511,9 +507,63 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">“Sheet中红色内容为样例，可以删除，但需要保留第一列表头，且表头名称不能修改。
+      <t xml:space="preserve">」工作表中的紅色內容為範例，可刪除，但須保留第一列的欄位名稱，且不可修改欄位名稱。
 </t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBM SAN-B24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAN交換器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78H1235</t>
+  </si>
+  <si>
+    <t>78H1236</t>
+  </si>
+  <si>
+    <t>78H1237</t>
+  </si>
+  <si>
+    <t>78H1238</t>
+  </si>
+  <si>
+    <t>78H1239</t>
+  </si>
+  <si>
+    <t>78H1240</t>
+  </si>
+  <si>
+    <t>78H1241</t>
+  </si>
+  <si>
+    <t>78H1242</t>
+  </si>
+  <si>
+    <t>78H1243</t>
+  </si>
+  <si>
+    <t>78H1244</t>
+  </si>
+  <si>
+    <t>IPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>語音設備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWAYA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rack-web.szqp.site</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -699,6 +749,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -713,18 +775,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1067,9 +1117,9 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="11" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="11"/>
-    <col min="8" max="8" width="41.83203125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="6"/>
+    <col min="8" max="8" width="41.83203125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1088,13 +1138,13 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1114,13 +1164,13 @@
       <c r="E2" s="2">
         <v>2</v>
       </c>
-      <c r="F2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2" s="9">
+      <c r="F2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="4">
         <v>123456</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1140,14 +1190,14 @@
       <c r="E3" s="2">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>46</v>
+      <c r="H3" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1166,9 +1216,13 @@
       <c r="E4" s="2">
         <v>11</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
@@ -1186,14 +1240,14 @@
       <c r="E5" s="2">
         <v>19</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>47</v>
+      <c r="H5" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1212,9 +1266,13 @@
       <c r="E6" s="2">
         <v>22</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="F6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
@@ -1232,9 +1290,11 @@
       <c r="E7" s="2">
         <v>35</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
@@ -1252,9 +1312,11 @@
       <c r="E8" s="2">
         <v>42</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
@@ -1272,9 +1334,11 @@
       <c r="E9" s="2">
         <v>4</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
@@ -1292,9 +1356,11 @@
       <c r="E10" s="2">
         <v>15</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
@@ -1312,9 +1378,11 @@
       <c r="E11" s="2">
         <v>42</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
@@ -1332,9 +1400,11 @@
       <c r="E12" s="2">
         <v>6</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
@@ -1352,9 +1422,11 @@
       <c r="E13" s="2">
         <v>18</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
@@ -1372,13 +1444,15 @@
       <c r="E14" s="2">
         <v>12</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>19</v>
@@ -1392,9 +1466,15 @@
       <c r="E15" s="2">
         <v>4</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
+      <c r="F15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1412,162 +1492,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="40" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="A1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="A2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="A3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/example-zh-tw.xlsx
+++ b/example-zh-tw.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qp/chatgpt/rack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A9E55F-3D6F-9E40-9C1C-F50BDF270521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A5BA32-8574-CB40-99DE-4AA37A090831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16860" activeTab="1" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
   </bookViews>
@@ -693,7 +693,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -703,6 +703,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -743,9 +749,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -775,6 +778,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1117,362 +1123,362 @@
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" style="6"/>
-    <col min="8" max="8" width="41.83203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="5"/>
+    <col min="8" max="8" width="41.83203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>123456</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="17">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>8</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>11</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>15</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>20</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>30</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>40</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>42</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="4"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>7</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>15</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>41</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>42</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="4"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>9</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>18</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="3"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>10</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>12</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>4</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1492,162 +1498,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="40" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
